--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="96" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B5AA3D1B-3B37-4B71-98DF-786A1F9E8F40}"/>
+  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E503D256-3270-459A-9275-A820754EFA78}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -125,9 +125,6 @@
     <t>Requiere un número mínimo de participantes y un espacio adecuado para las actividades prácticas.</t>
   </si>
   <si>
-    <t>Requiere Equipo del Herbario</t>
-  </si>
-  <si>
     <t>Si/no</t>
   </si>
   <si>
@@ -204,13 +201,64 @@
   </si>
   <si>
     <t>Santa Feliz herbario@unphu.edu.do</t>
+  </si>
+  <si>
+    <t>Analisis Quimico</t>
+  </si>
+  <si>
+    <t>Determinación del contenido de polifenoles en extractos de productos naturales por espectrofotometría UV-VIS</t>
+  </si>
+  <si>
+    <t>Laboratorio de Investigaciones en Ciencias Básicas</t>
+  </si>
+  <si>
+    <t>Requiere Equipo del Laboratorio</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas</t>
+  </si>
+  <si>
+    <t>Alberto Nuñez: alnunez@unphu.edu.do</t>
+  </si>
+  <si>
+    <t>Determinación de polifenoles en extractos de productos naturales por cromatografía líquida de alta resolución (HPLC).</t>
+  </si>
+  <si>
+    <t>Determinación de flavonoides en alimentos por cromatografía líquida de alta resolución (HPLC)</t>
+  </si>
+  <si>
+    <t>Determinación de principios activos farmacéuticos en formulaciones galénicas por HPLC</t>
+  </si>
+  <si>
+    <t>Determinación de principios activos farmacéuticos en muestras de fluidos biológicos por HPLC.</t>
+  </si>
+  <si>
+    <t>Determinación de pureza de productos químicos por técnicas cromatográficas (HPLC)</t>
+  </si>
+  <si>
+    <t>Aislamiento y purificación de principios activos a partir de mezclas obtenidas por síntesis química o extracción de productos naturales</t>
+  </si>
+  <si>
+    <t>Valorización del aprovechamiento de residuos agroalimentarios y forestales para la producción de productos de alto valor agregado.</t>
+  </si>
+  <si>
+    <t>Implementación de Sistemas de Garantía de Calidad para el Análisis y Control de Procesos Productivos.</t>
+  </si>
+  <si>
+    <t>Diseño, coordinación y monitoreo de ensayos clínicos para la evaluación de la eficacia y seguridad de productos farmacéuticos (Fases I, II y III)</t>
+  </si>
+  <si>
+    <t>Diseño de Protocolos y Proyectos de Investigación-Desarrollo en diferentes campos de la Ciencia y la Tecnología.</t>
+  </si>
+  <si>
+    <t>Análisis del Estado del Arte, Nichos de Mercado y Direcciones Estratégicas de Investigación en Ciencias Básicas y Aplicadas.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -231,6 +279,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -265,10 +321,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -283,8 +340,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -586,10 +645,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="33" customWidth="1"/>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -605,13 +665,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -640,13 +700,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>13</v>
@@ -675,13 +735,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>20</v>
@@ -710,34 +770,34 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>12</v>
       </c>
       <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -745,34 +805,34 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="J5" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="105" x14ac:dyDescent="0.25">
@@ -780,34 +840,241 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>49</v>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -833,17 +1100,32 @@
       <formula1>listaS</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" display="alnunez@unphu.edu.do" xr:uid="{09C99202-9552-4F98-98DE-68801413754A}"/>
+    <hyperlink ref="B8" r:id="rId2" display="alnunez@unphu.edu.do" xr:uid="{0E1A8D9C-C515-4F57-ABCE-AA52629D9F07}"/>
+    <hyperlink ref="B9" r:id="rId3" display="alnunez@unphu.edu.do" xr:uid="{DE972DF2-4DD8-4D8F-B4B2-7A0338403B2B}"/>
+    <hyperlink ref="B10" r:id="rId4" display="alnunez@unphu.edu.do" xr:uid="{F71B584C-738D-4887-80E0-E9F5F028F305}"/>
+    <hyperlink ref="B11" r:id="rId5" display="alnunez@unphu.edu.do" xr:uid="{386440C9-B821-42E9-9C35-5596908D7430}"/>
+    <hyperlink ref="B12" r:id="rId6" display="alnunez@unphu.edu.do" xr:uid="{42B2DC46-29CD-44E2-8B7E-A27B705F6E73}"/>
+    <hyperlink ref="B13" r:id="rId7" display="alnunez@unphu.edu.do" xr:uid="{F1D91BA9-2B52-4E46-A7ED-66DA2697F52B}"/>
+    <hyperlink ref="B14" r:id="rId8" display="alnunez@unphu.edu.do" xr:uid="{86B1AF36-3D6A-4851-88EC-E15AD611FDC4}"/>
+    <hyperlink ref="B15" r:id="rId9" display="alnunez@unphu.edu.do" xr:uid="{110B4970-8F4A-4A14-A237-28D4756B4267}"/>
+    <hyperlink ref="B16" r:id="rId10" display="alnunez@unphu.edu.do" xr:uid="{72A6886C-C407-4FF8-A6A0-7D2F3242D502}"/>
+    <hyperlink ref="B17" r:id="rId11" display="alnunez@unphu.edu.do" xr:uid="{03313421-0E49-4646-BBB8-CE35126DA7FD}"/>
+    <hyperlink ref="B18" r:id="rId12" display="alnunez@unphu.edu.do" xr:uid="{D53364F5-C00F-4A56-B88F-FC46E4F052F5}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId13"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E6260D-E141-4E01-9DD9-6796BD13D20A}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -854,7 +1136,7 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -865,15 +1147,23 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>53</v>
+      </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{E503D256-3270-459A-9275-A820754EFA78}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EEC9AF3A-2438-4E4C-A2AC-F7F9E651C3D3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -252,6 +252,15 @@
   </si>
   <si>
     <t>Análisis del Estado del Arte, Nichos de Mercado y Direcciones Estratégicas de Investigación en Ciencias Básicas y Aplicadas.</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -886,8 +895,23 @@
       <c r="E7" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="F7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>68</v>
+      </c>
       <c r="I7" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -906,6 +930,24 @@
       <c r="E8" s="4" t="s">
         <v>57</v>
       </c>
+      <c r="F8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -923,6 +965,24 @@
       <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
+      <c r="F9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -940,6 +1000,24 @@
       <c r="E10" s="4" t="s">
         <v>59</v>
       </c>
+      <c r="F10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -957,6 +1035,24 @@
       <c r="E11" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="F11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -974,6 +1070,24 @@
       <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="F12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
@@ -991,6 +1105,24 @@
       <c r="E13" s="4" t="s">
         <v>62</v>
       </c>
+      <c r="F13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -1008,6 +1140,24 @@
       <c r="E14" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="F14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -1025,6 +1175,24 @@
       <c r="E15" s="4" t="s">
         <v>64</v>
       </c>
+      <c r="F15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -1042,8 +1210,26 @@
       <c r="E16" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="F16" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>53</v>
       </c>
@@ -1059,8 +1245,26 @@
       <c r="E17" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="F17" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -1075,6 +1279,24 @@
       </c>
       <c r="E18" s="4" t="s">
         <v>67</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\portal_servicios_github\portal_servicios_github\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EEC9AF3A-2438-4E4C-A2AC-F7F9E651C3D3}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{07F76A29-A6C5-49C3-ADF6-FA9005F3F650}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="72">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas.</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
         <v>70</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>68</v>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\portal_servicios_github\portal_servicios_github\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{07F76A29-A6C5-49C3-ADF6-FA9005F3F650}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B2A5C09D-C861-4DBB-8197-59D9A57E2FA2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="97">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -263,7 +263,91 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas.</t>
+    <t>Laboratorio de Investigación de Ciencias Biológicas</t>
+  </si>
+  <si>
+    <t>Enmanuel Antonio Montero emontero@unphu.edu.do</t>
+  </si>
+  <si>
+    <t>Consultoras ambientales, empresas de la pesca ornamental y acuicolas, instituciones públicas, ONG, universidades,  investigadores</t>
+  </si>
+  <si>
+    <t>Servicio 1. Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivos y materiales/cristaleria
+ para colecta y preservación de muestras. </t>
+  </si>
+  <si>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros
+Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
+  </si>
+  <si>
+    <t>Expertos en biología pesquera y biología de conservación, 
+asistentes de campo (según el proyecto servicio ).</t>
+  </si>
+  <si>
+    <t>Variable, según el el interes del solicitante, del estudio y el alcance de este.</t>
+  </si>
+  <si>
+    <t>Servicio 2. Evaluación de salud de arrecifes de coral e invertebrados bentónicos. Especies exoticas ivasoras acuaticas, organismos ornametales y de trafico para industria de acuarios</t>
+  </si>
+  <si>
+    <t>Consultoras ambientales, empresas turisticas, de la pesca ornamenta y otras que implementan la economia azul, instituciones públicas, ONG, universidades,  investigadores</t>
+  </si>
+  <si>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi balanza, 
+multiparamétrico, correntómetro, dron,  estaciones autónomas de monitoreo biológico marino (ARMS), equipo de buceo y embarcación. 
+Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivos y materiales/cristaleria para colecta y preservación de muestras,
+ material de montaje de especímenes. </t>
+  </si>
+  <si>
+    <t>Expertos en biología pesquera, biología de conservación y 
+asistentes de campo.</t>
+  </si>
+  <si>
+    <t>Servicio 3. Extracción y Purificación de ADN (Tejidos y eDNA)</t>
+  </si>
+  <si>
+    <t>Equipos de laboratorio: centrífuga, autoclave, Balanza analítica de calibración externa, Incubadora de seguridad de protocolo avanzado, agitador vórtex digital, termociclador, nevera y congelador.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactivos, materiales y cristaleria para la extracion del ADN,
+ material de montaje de especímenes. </t>
+  </si>
+  <si>
+    <t>Servicio 4.Amplifición  de ADN (Tejidos y eDNA)</t>
+  </si>
+  <si>
+    <t>Reactivos, materiales y cristaleria para la extracion del ADN,
+ material de montaje de especímenes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experta en biologia molecular  </t>
+  </si>
+  <si>
+    <t>Taller técnicas de muestreo de campo en investigaciones de especies marinas pesqueras</t>
+  </si>
+  <si>
+    <t>Bases para el diseño metodológico de técnicas moleculares para estudios de macrofauna</t>
+  </si>
+  <si>
+    <t>Instituciones públicas y privadas, universidades y publico en general</t>
+  </si>
+  <si>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros</t>
+  </si>
+  <si>
+    <t>Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
+  </si>
+  <si>
+    <t>Material didáctico y recursos audiovisuales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
   </si>
 </sst>
 </file>
@@ -657,11 +741,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
@@ -1293,17 +1377,227 @@
         <v>70</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>68</v>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="315" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="225" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="225" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="165" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K24" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:O60">
+  <conditionalFormatting sqref="A1:O57">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -1315,13 +1609,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A70" xr:uid="{D8DECFFA-5CBE-4E0D-8A27-6C55887A2999}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A67" xr:uid="{D8DECFFA-5CBE-4E0D-8A27-6C55887A2999}">
       <formula1>listaLab</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C60" xr:uid="{70FEB337-C351-4F50-AE87-030127DE8B64}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C57" xr:uid="{70FEB337-C351-4F50-AE87-030127DE8B64}">
       <formula1>listaServicios</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D60" xr:uid="{6CDCAB9A-F482-4EC0-9315-59F984EF0DA1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D57" xr:uid="{6CDCAB9A-F482-4EC0-9315-59F984EF0DA1}">
       <formula1>listaS</formula1>
     </dataValidation>
   </dataValidations>
@@ -1387,6 +1681,9 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>71</v>
+      </c>
       <c r="B4" t="s">
         <v>51</v>
       </c>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\portal_servicios_github\portal_servicios_github\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B2A5C09D-C861-4DBB-8197-59D9A57E2FA2}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{70DB1EE3-6FC4-4256-9F2E-2E6BE171BDB2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,9 +272,6 @@
     <t>Consultoras ambientales, empresas de la pesca ornamental y acuicolas, instituciones públicas, ONG, universidades,  investigadores</t>
   </si>
   <si>
-    <t>Servicio 1. Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reactivos y materiales/cristaleria
  para colecta y preservación de muestras. </t>
   </si>
@@ -283,14 +280,7 @@
 Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
   </si>
   <si>
-    <t>Expertos en biología pesquera y biología de conservación, 
-asistentes de campo (según el proyecto servicio ).</t>
-  </si>
-  <si>
     <t>Variable, según el el interes del solicitante, del estudio y el alcance de este.</t>
-  </si>
-  <si>
-    <t>Servicio 2. Evaluación de salud de arrecifes de coral e invertebrados bentónicos. Especies exoticas ivasoras acuaticas, organismos ornametales y de trafico para industria de acuarios</t>
   </si>
   <si>
     <t>Consultoras ambientales, empresas turisticas, de la pesca ornamenta y otras que implementan la economia azul, instituciones públicas, ONG, universidades,  investigadores</t>
@@ -309,9 +299,6 @@
 asistentes de campo.</t>
   </si>
   <si>
-    <t>Servicio 3. Extracción y Purificación de ADN (Tejidos y eDNA)</t>
-  </si>
-  <si>
     <t>Equipos de laboratorio: centrífuga, autoclave, Balanza analítica de calibración externa, Incubadora de seguridad de protocolo avanzado, agitador vórtex digital, termociclador, nevera y congelador.</t>
   </si>
   <si>
@@ -319,35 +306,48 @@
  material de montaje de especímenes. </t>
   </si>
   <si>
-    <t>Servicio 4.Amplifición  de ADN (Tejidos y eDNA)</t>
+    <t xml:space="preserve">Experta en biologia molecular  </t>
+  </si>
+  <si>
+    <t>Taller técnicas de muestreo de campo en investigaciones de especies marinas pesqueras</t>
+  </si>
+  <si>
+    <t>Bases para el diseño metodológico de técnicas moleculares para estudios de macrofauna</t>
+  </si>
+  <si>
+    <t>Instituciones públicas y privadas, universidades y publico en general</t>
+  </si>
+  <si>
+    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros</t>
+  </si>
+  <si>
+    <t>Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
+  </si>
+  <si>
+    <t>Material didáctico y recursos audiovisuales</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
   </si>
   <si>
     <t>Reactivos, materiales y cristaleria para la extracion del ADN,
- material de montaje de especímenes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experta en biologia molecular  </t>
-  </si>
-  <si>
-    <t>Taller técnicas de muestreo de campo en investigaciones de especies marinas pesqueras</t>
-  </si>
-  <si>
-    <t>Bases para el diseño metodológico de técnicas moleculares para estudios de macrofauna</t>
-  </si>
-  <si>
-    <t>Instituciones públicas y privadas, universidades y publico en general</t>
-  </si>
-  <si>
-    <t>Equipos de campo: GPS, cámara subacuáfica, red de plancton , ictiómetro, disco de secchi, flujómetro, balanza, multiparamétrico, correntómetro, dron, entre otros</t>
-  </si>
-  <si>
-    <t>Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
-  </si>
-  <si>
-    <t>Material didáctico y recursos audiovisuales</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
+ material de montaje de especímenes</t>
+  </si>
+  <si>
+    <t>Expertos en biología pesquera y biología de conservación, 
+asistentes de campo (según el proyecto servicio )</t>
+  </si>
+  <si>
+    <t>Amplifición  de ADN (Tejidos y eDNA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
+  </si>
+  <si>
+    <t>Evaluación de salud de arrecifes de coral e invertebrados bentónicos. Especies exoticas ivasoras acuaticas, organismos ornametales y de trafico para industria de acuarios</t>
+  </si>
+  <si>
+    <t>Extracción y Purificación de ADN (Tejidos y eDNA)</t>
   </si>
 </sst>
 </file>
@@ -1400,22 +1400,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>19</v>
@@ -1435,22 +1435,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="I20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>19</v>
@@ -1470,22 +1470,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>19</v>
@@ -1505,22 +1505,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>19</v>
@@ -1540,19 +1540,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>41</v>
@@ -1575,19 +1575,19 @@
         <v>29</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>41</v>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\portal_servicios_github\portal_servicios_github\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{70DB1EE3-6FC4-4256-9F2E-2E6BE171BDB2}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D1381AA9-2065-4C84-9958-702C034C0B14}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="108">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -272,6 +272,9 @@
     <t>Consultoras ambientales, empresas de la pesca ornamental y acuicolas, instituciones públicas, ONG, universidades,  investigadores</t>
   </si>
   <si>
+    <t>Servicio 1. Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reactivos y materiales/cristaleria
  para colecta y preservación de muestras. </t>
   </si>
@@ -280,7 +283,14 @@
 Equipos de laboratorio. Estereoscopio, microscopio y equipos informáticos.</t>
   </si>
   <si>
+    <t>Expertos en biología pesquera y biología de conservación, 
+asistentes de campo (según el proyecto servicio ).</t>
+  </si>
+  <si>
     <t>Variable, según el el interes del solicitante, del estudio y el alcance de este.</t>
+  </si>
+  <si>
+    <t>Servicio 2. Evaluación de salud de arrecifes de coral e invertebrados bentónicos. Especies exoticas ivasoras acuaticas, organismos ornametales y de trafico para industria de acuarios</t>
   </si>
   <si>
     <t>Consultoras ambientales, empresas turisticas, de la pesca ornamenta y otras que implementan la economia azul, instituciones públicas, ONG, universidades,  investigadores</t>
@@ -299,6 +309,9 @@
 asistentes de campo.</t>
   </si>
   <si>
+    <t>Servicio 3. Extracción y Purificación de ADN (Tejidos y eDNA)</t>
+  </si>
+  <si>
     <t>Equipos de laboratorio: centrífuga, autoclave, Balanza analítica de calibración externa, Incubadora de seguridad de protocolo avanzado, agitador vórtex digital, termociclador, nevera y congelador.</t>
   </si>
   <si>
@@ -306,6 +319,13 @@
  material de montaje de especímenes. </t>
   </si>
   <si>
+    <t>Servicio 4.Amplifición  de ADN (Tejidos y eDNA)</t>
+  </si>
+  <si>
+    <t>Reactivos, materiales y cristaleria para la extracion del ADN,
+ material de montaje de especímenes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Experta en biologia molecular  </t>
   </si>
   <si>
@@ -330,24 +350,39 @@
     <t xml:space="preserve"> Personal del laboratorio de Ciencias Biológicas</t>
   </si>
   <si>
-    <t>Reactivos, materiales y cristaleria para la extracion del ADN,
- material de montaje de especímenes</t>
-  </si>
-  <si>
-    <t>Expertos en biología pesquera y biología de conservación, 
-asistentes de campo (según el proyecto servicio )</t>
-  </si>
-  <si>
-    <t>Amplifición  de ADN (Tejidos y eDNA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Asesoría técnica y levantamiento de información sobre  recursos ícticos y pesquerías</t>
-  </si>
-  <si>
-    <t>Evaluación de salud de arrecifes de coral e invertebrados bentónicos. Especies exoticas ivasoras acuaticas, organismos ornametales y de trafico para industria de acuarios</t>
-  </si>
-  <si>
-    <t>Extracción y Purificación de ADN (Tejidos y eDNA)</t>
+    <t xml:space="preserve"> Laboratorio de Investigaciones de la Facultad de Ciencias y Tecnología</t>
+  </si>
+  <si>
+    <t>Análisis de composición</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Laboratorio de Ciencias y Tecnología</t>
+  </si>
+  <si>
+    <t>Ramón Alonso Pérez Romero rperez@unphu.edu.do</t>
+  </si>
+  <si>
+    <t>Determinación de los parámetros de composición proximal (humedad, cenizas, proteína cruda, grasa cruda, fibra cruda/NDF/ADF/ADL y carbohidratos por diferencia) en muestras alimenticias, agropecuarias o materias primas, mediante métodos estandarizados. Incluye preparación de la muestra, ejecución del análisis y entrega de reporte de resultados.</t>
+  </si>
+  <si>
+    <t>Empresas del sector de alimentos y agroindustria, productores agropecuarios, entidades regulatorias, investigadores enfocados en valorización de biomasa residual o alimentos poco convencionales.</t>
+  </si>
+  <si>
+    <t>Balanza analítica; Tamizador motorizado; Desintegrador MPD-102; Medidor rápido de humedad BM-50-1; 
+Horno; Mufla; Sistema Soxhlet BFA-1S; Analizador Kjeldahl AKN-10S; Analizador de fibra BK-F800; 
+Digestor de grafito GDA-20; Agitadores magnéticos; Placa caliente auxiliar.</t>
+  </si>
+  <si>
+    <t>Grasa cruda (Soxhlet): n-Hexano o ciclohexano grado HPLC, agua destilada. Fibra cruda/NDF/ADF/ADL (BK-F800): H₂SO₄ 1.25%, NaOH 1.25%, acetona ≥99.5%, solución detergente neutra (SDS, EDTA, borato), Na₂SO₃ (opcional), α-amilasa termoestable, solución detergente ácida (CTAB + H₂SO₄), H₂SO₄ 72%. Proteína (Kjeldahl): H₂SO₄ 98%, catalizador Kjeldahl (K₂SO₄:CuSO₄/Se), NaOH 40%, H₃BO₃ 4% + indicador, ácido estándar HCl 0.1N. Humedad y Cenizas: sin reactivos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Personal técnico de laboratorio dedicado a estas actividades. No se asignan estudiantes, salvo que desempeñen una función específica dentro del servicio.</t>
+  </si>
+  <si>
+    <t>Varía según el ensayo: Humedad (aprox. 4–6 h, incluyendo secado y enfriamiento); Cenizas (aprox. 6–8 h en mufla, más enfriamiento); Grasa cruda/Soxhlet (aprox. 4–6 h); Proteína/Kjeldahl (aprox. 3–5 h entre digestión, destilación y titulación); Fibra cruda/NDF/ADF/ADL (aprox. 3–4 h por fracción). Para un panel completo de composición proximal, el tiempo total estimado es de 3 a 5 días laborables, considerando preparación de muestra, corridas por lote y elaboración del reporte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No se aceptan muestras de carnes, pescados u otros productos de origen cárnico/pesquero. El laboratorio está enfocado prioritariamente en la valorización de biomasa residual y alimentos poco convencionales.</t>
   </si>
 </sst>
 </file>
@@ -741,12 +776,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="31.5703125" customWidth="1"/>
     <col min="6" max="6" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1400,22 +1436,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>19</v>
@@ -1435,22 +1471,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>19</v>
@@ -1470,22 +1506,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>19</v>
@@ -1505,22 +1541,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>19</v>
@@ -1540,19 +1576,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>41</v>
@@ -1575,25 +1611,60 @@
         <v>29</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>41</v>
       </c>
       <c r="K24" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="255" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1640,11 +1711,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90E6260D-E141-4E01-9DD9-6796BD13D20A}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="64.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1688,6 +1759,14 @@
         <v>51</v>
       </c>
     </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/datos/Servicios.xlsx
+++ b/datos/Servicios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wramirez\OneDrive\UNPHU\laboratorios\servicios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D1381AA9-2065-4C84-9958-702C034C0B14}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="11_AD4D2F04E46CFB4ACB3E20CE25D7F7F0683EDF26" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{D78FB0B7-617F-4778-A123-3ED4049230CD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="110">
   <si>
     <t>Laboratorio</t>
   </si>
@@ -213,9 +213,6 @@
   </si>
   <si>
     <t>Requiere Equipo del Laboratorio</t>
-  </si>
-  <si>
-    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas</t>
   </si>
   <si>
     <t>Alberto Nuñez: alnunez@unphu.edu.do</t>
@@ -383,6 +380,15 @@
   </si>
   <si>
     <t xml:space="preserve"> No se aceptan muestras de carnes, pescados u otros productos de origen cárnico/pesquero. El laboratorio está enfocado prioritariamente en la valorización de biomasa residual y alimentos poco convencionales.</t>
+  </si>
+  <si>
+    <t>Farmaceuticas, Laboratorios</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio</t>
+  </si>
+  <si>
+    <t>Personal del Laboratorio de Investigaciones en Ciencias Básicas (pendiente de contracion)</t>
   </si>
 </sst>
 </file>
@@ -1007,7 +1013,7 @@
         <v>53</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>51</v>
@@ -1019,22 +1025,22 @@
         <v>52</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1042,7 +1048,7 @@
         <v>53</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
@@ -1051,33 +1057,33 @@
         <v>29</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>51</v>
@@ -1086,33 +1092,33 @@
         <v>29</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
@@ -1121,25 +1127,25 @@
         <v>29</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1147,7 +1153,7 @@
         <v>53</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
         <v>51</v>
@@ -1156,33 +1162,33 @@
         <v>29</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>53</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
@@ -1191,25 +1197,25 @@
         <v>29</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -1217,7 +1223,7 @@
         <v>53</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
@@ -1226,25 +1232,25 @@
         <v>29</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>68</v>
+        <v>107</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -1252,7 +1258,7 @@
         <v>53</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -1261,25 +1267,25 @@
         <v>28</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I14" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1287,7 +1293,7 @@
         <v>53</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
@@ -1296,25 +1302,25 @@
         <v>28</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I15" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="75" x14ac:dyDescent="0.25">
@@ -1322,7 +1328,7 @@
         <v>53</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
         <v>11</v>
@@ -1331,25 +1337,25 @@
         <v>28</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="H16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I16" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1357,7 +1363,7 @@
         <v>53</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
         <v>11</v>
@@ -1366,25 +1372,25 @@
         <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I17" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="60" x14ac:dyDescent="0.25">
@@ -1392,7 +1398,7 @@
         <v>53</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
         <v>11</v>
@@ -1401,33 +1407,33 @@
         <v>28</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="H18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" t="s">
         <v>71</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
       </c>
       <c r="C19" t="s">
         <v>11</v>
@@ -1436,22 +1442,22 @@
         <v>29</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>19</v>
@@ -1459,10 +1465,10 @@
     </row>
     <row r="20" spans="1:11" ht="315" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" t="s">
         <v>71</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
       </c>
       <c r="C20" t="s">
         <v>11</v>
@@ -1471,22 +1477,22 @@
         <v>29</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="G20" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>83</v>
-      </c>
       <c r="J20" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>19</v>
@@ -1494,10 +1500,10 @@
     </row>
     <row r="21" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
         <v>71</v>
-      </c>
-      <c r="B21" t="s">
-        <v>72</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -1506,22 +1512,22 @@
         <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="I21" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>19</v>
@@ -1529,10 +1535,10 @@
     </row>
     <row r="22" spans="1:11" ht="225" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
         <v>71</v>
-      </c>
-      <c r="B22" t="s">
-        <v>72</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
@@ -1541,22 +1547,22 @@
         <v>29</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>19</v>
@@ -1564,10 +1570,10 @@
     </row>
     <row r="23" spans="1:11" ht="165" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
         <v>71</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1576,19 +1582,19 @@
         <v>29</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="H23" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>41</v>
@@ -1599,10 +1605,10 @@
     </row>
     <row r="24" spans="1:11" ht="90" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
         <v>71</v>
-      </c>
-      <c r="B24" t="s">
-        <v>72</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1611,19 +1617,19 @@
         <v>29</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="G24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>41</v>
@@ -1634,37 +1640,37 @@
     </row>
     <row r="25" spans="1:11" ht="255" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>98</v>
       </c>
       <c r="D25" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1759,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" t="s">
         <v>51</v>
@@ -1761,10 +1767,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
